--- a/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_398_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_398_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="L2" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="M2" t="n">
         <v>5</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="L3" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>16</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>03:41</t>
         </is>
       </c>
       <c r="AN17" t="n">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>25.7%</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
@@ -1461,7 +1461,7 @@
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>37.4%</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
@@ -1531,7 +1531,7 @@
         <v>8</v>
       </c>
       <c r="T18" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>38:53</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AN18" t="n">
@@ -1647,22 +1647,22 @@
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>12.0%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>5.1%</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>7.2%</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>7.6%</t>
+          <t>17.7%</t>
         </is>
       </c>
     </row>
@@ -1727,16 +1727,16 @@
         <v>9</v>
       </c>
       <c r="T19" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>5</v>
@@ -1795,7 +1795,7 @@
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>65:38</t>
+          <t>35:50</t>
         </is>
       </c>
       <c r="AN19" t="n">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>20.1%</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
@@ -1853,12 +1853,12 @@
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>6.3%</t>
+          <t>11.5%</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>2.2%</t>
+          <t>4.2%</t>
         </is>
       </c>
     </row>
@@ -1991,7 +1991,7 @@
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>10:19</t>
+          <t>00:19</t>
         </is>
       </c>
       <c r="AN20" t="n">
@@ -2187,7 +2187,7 @@
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>21:22</t>
+          <t>01:22</t>
         </is>
       </c>
       <c r="AN21" t="n">
@@ -2321,10 +2321,10 @@
         <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
         <v>2</v>
@@ -2383,7 +2383,7 @@
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>53:17</t>
+          <t>23:28</t>
         </is>
       </c>
       <c r="AN22" t="n">
@@ -2431,22 +2431,22 @@
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>8.0%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>1.8%</t>
+          <t>4.2%</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>23.5%</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>7.4%</t>
         </is>
       </c>
     </row>
@@ -2514,7 +2514,7 @@
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2579,7 +2579,7 @@
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>40:07</t>
+          <t>20:08</t>
         </is>
       </c>
       <c r="AN23" t="n">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>5.9%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>4.8%</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>14.2%</t>
         </is>
       </c>
     </row>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="AM24" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>02:39</t>
         </is>
       </c>
       <c r="AN24" t="n">
@@ -2823,7 +2823,7 @@
       </c>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>17.9%</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
@@ -2903,7 +2903,7 @@
         <v>38</v>
       </c>
       <c r="T25" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
@@ -2971,7 +2971,7 @@
       </c>
       <c r="AM25" t="inlineStr">
         <is>
-          <t>43:26</t>
+          <t>33:24</t>
         </is>
       </c>
       <c r="AN25" t="n">
@@ -3019,22 +3019,22 @@
       </c>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>4.5%</t>
+          <t>5.8%</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>20.6%</t>
         </is>
       </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>39.9%</t>
+          <t>54.9%</t>
         </is>
       </c>
     </row>
@@ -3167,7 +3167,7 @@
       </c>
       <c r="AM26" t="inlineStr">
         <is>
-          <t>50:39</t>
+          <t>20:54</t>
         </is>
       </c>
       <c r="AN26" t="n">
@@ -3215,17 +3215,17 @@
       </c>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>1.9%</t>
+          <t>4.7%</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
-          <t>2.7%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="AZ26" t="inlineStr">
@@ -3295,16 +3295,16 @@
         <v>36</v>
       </c>
       <c r="T27" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="U27" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="V27" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="W27" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X27" t="n">
         <v>13</v>
@@ -3363,7 +3363,7 @@
       </c>
       <c r="AM27" t="inlineStr">
         <is>
-          <t>42:57</t>
+          <t>32:55</t>
         </is>
       </c>
       <c r="AN27" t="n">
@@ -3411,22 +3411,22 @@
       </c>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>25.1%</t>
+          <t>32.7%</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>11.9%</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>12.6%</t>
         </is>
       </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>5.5%</t>
+          <t>9.4%</t>
         </is>
       </c>
     </row>
@@ -3827,16 +3827,16 @@
         <v>103</v>
       </c>
       <c r="T30" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="U30" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="V30" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="W30" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="X30" t="n">
         <v>32</v>
@@ -4295,13 +4295,13 @@
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V35" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X35" t="n">
         <v>2</v>
@@ -4360,7 +4360,7 @@
       </c>
       <c r="AM35" t="inlineStr">
         <is>
-          <t>47:10</t>
+          <t>17:24</t>
         </is>
       </c>
       <c r="AN35" t="n">
@@ -4408,22 +4408,22 @@
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>26.7%</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>7.9%</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
-          <t>4.1%</t>
+          <t>11.2%</t>
         </is>
       </c>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>2.9%</t>
+          <t>9.7%</t>
         </is>
       </c>
     </row>
@@ -4556,7 +4556,7 @@
       </c>
       <c r="AM36" t="inlineStr">
         <is>
-          <t>35:02</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AN36" t="n">
@@ -4604,17 +4604,17 @@
       </c>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>5.3%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>9.2%</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
-          <t>2.8%</t>
+          <t>6.5%</t>
         </is>
       </c>
       <c r="AZ36" t="inlineStr">
@@ -4690,10 +4690,10 @@
         <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="W37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X37" t="n">
         <v>3</v>
@@ -4752,7 +4752,7 @@
       </c>
       <c r="AM37" t="inlineStr">
         <is>
-          <t>45:11</t>
+          <t>25:09</t>
         </is>
       </c>
       <c r="AN37" t="n">
@@ -4800,22 +4800,22 @@
       </c>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>21.1%</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>3.1%</t>
+          <t>5.5%</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>21.0%</t>
+          <t>41.8%</t>
         </is>
       </c>
     </row>
@@ -4883,7 +4883,7 @@
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -4948,7 +4948,7 @@
       </c>
       <c r="AM38" t="inlineStr">
         <is>
-          <t>37:54</t>
+          <t>17:55</t>
         </is>
       </c>
       <c r="AN38" t="n">
@@ -4996,17 +4996,17 @@
       </c>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>6.0%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>7.3%</t>
+          <t>15.4%</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
-          <t>2.6%</t>
+          <t>5.4%</t>
         </is>
       </c>
       <c r="AZ38" t="inlineStr">
@@ -5144,7 +5144,7 @@
       </c>
       <c r="AM39" t="inlineStr">
         <is>
-          <t>10:05</t>
+          <t>00:05</t>
         </is>
       </c>
       <c r="AN39" t="n">
@@ -5278,10 +5278,10 @@
         <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="W40" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X40" t="n">
         <v>7</v>
@@ -5340,7 +5340,7 @@
       </c>
       <c r="AM40" t="inlineStr">
         <is>
-          <t>42:57</t>
+          <t>22:55</t>
         </is>
       </c>
       <c r="AN40" t="n">
@@ -5388,7 +5388,7 @@
       </c>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>14.8%</t>
+          <t>27.7%</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
@@ -5398,12 +5398,12 @@
       </c>
       <c r="AY40" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>20.1%</t>
         </is>
       </c>
     </row>
@@ -5474,10 +5474,10 @@
         <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W41" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="X41" t="n">
         <v>5</v>
@@ -5536,7 +5536,7 @@
       </c>
       <c r="AM41" t="inlineStr">
         <is>
-          <t>24:32</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AN41" t="n">
@@ -5584,7 +5584,7 @@
       </c>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>21.5%</t>
+          <t>35.6%</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
@@ -5594,12 +5594,12 @@
       </c>
       <c r="AY41" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>13.1%</t>
+          <t>27.8%</t>
         </is>
       </c>
     </row>
@@ -5667,7 +5667,7 @@
         <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -5732,7 +5732,7 @@
       </c>
       <c r="AM42" t="inlineStr">
         <is>
-          <t>41:54</t>
+          <t>22:05</t>
         </is>
       </c>
       <c r="AN42" t="n">
@@ -5780,22 +5780,22 @@
       </c>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>3.3%</t>
+          <t>6.3%</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>6.6%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
-          <t>9.3%</t>
+          <t>17.7%</t>
         </is>
       </c>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>3.0%</t>
+          <t>5.8%</t>
         </is>
       </c>
     </row>
@@ -5863,7 +5863,7 @@
         <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -5928,7 +5928,7 @@
       </c>
       <c r="AM43" t="inlineStr">
         <is>
-          <t>44:14</t>
+          <t>24:25</t>
         </is>
       </c>
       <c r="AN43" t="n">
@@ -5976,17 +5976,17 @@
       </c>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>10.5%</t>
+          <t>19.0%</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>6.2%</t>
+          <t>11.3%</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
-          <t>8.8%</t>
+          <t>16.0%</t>
         </is>
       </c>
       <c r="AZ43" t="inlineStr">
@@ -6252,16 +6252,16 @@
         <v>10</v>
       </c>
       <c r="T45" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U45" t="n">
         <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="W45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="X45" t="n">
         <v>5</v>
@@ -6320,7 +6320,7 @@
       </c>
       <c r="AM45" t="inlineStr">
         <is>
-          <t>41:03</t>
+          <t>21:14</t>
         </is>
       </c>
       <c r="AN45" t="n">
@@ -6368,7 +6368,7 @@
       </c>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>23.8%</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
@@ -6378,12 +6378,12 @@
       </c>
       <c r="AY45" t="inlineStr">
         <is>
-          <t>7.1%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>16.7%</t>
+          <t>37.0%</t>
         </is>
       </c>
     </row>
@@ -6516,7 +6516,7 @@
       </c>
       <c r="AM46" t="inlineStr">
         <is>
-          <t>24:49</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AN46" t="n">
@@ -6564,22 +6564,22 @@
       </c>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>15.3%</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>18.6%</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>6.6%</t>
         </is>
       </c>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>5.1%</t>
+          <t>8.9%</t>
         </is>
       </c>
     </row>
@@ -6784,16 +6784,16 @@
         <v>120</v>
       </c>
       <c r="T48" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="U48" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="V48" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="W48" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="X48" t="n">
         <v>36</v>

--- a/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_398_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_398_EL.xlsx
@@ -662,13 +662,13 @@
         </is>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="K2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="M2" t="n">
         <v>5</v>
@@ -745,17 +745,17 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.67</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -821,13 +821,13 @@
         </is>
       </c>
       <c r="J3" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K3" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="M3" t="n">
         <v>16</v>
@@ -904,17 +904,17 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1531,7 +1531,7 @@
         <v>8</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
@@ -1727,16 +1727,16 @@
         <v>9</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U19" t="n">
         <v>0</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X19" t="n">
         <v>5</v>
@@ -2321,10 +2321,10 @@
         <v>0</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X22" t="n">
         <v>2</v>
@@ -2514,7 +2514,7 @@
         <v>0</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V23" t="n">
         <v>0</v>
@@ -2903,7 +2903,7 @@
         <v>38</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="U25" t="n">
         <v>0</v>
@@ -3295,16 +3295,16 @@
         <v>36</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X27" t="n">
         <v>13</v>
@@ -3827,16 +3827,16 @@
         <v>103</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="X30" t="n">
         <v>32</v>
@@ -4295,13 +4295,13 @@
         <v>0</v>
       </c>
       <c r="U35" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V35" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X35" t="n">
         <v>2</v>
@@ -4690,10 +4690,10 @@
         <v>0</v>
       </c>
       <c r="V37" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X37" t="n">
         <v>3</v>
@@ -4883,7 +4883,7 @@
         <v>0</v>
       </c>
       <c r="U38" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="V38" t="n">
         <v>0</v>
@@ -5278,10 +5278,10 @@
         <v>0</v>
       </c>
       <c r="V40" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="W40" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X40" t="n">
         <v>7</v>
@@ -5474,10 +5474,10 @@
         <v>0</v>
       </c>
       <c r="V41" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W41" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X41" t="n">
         <v>5</v>
@@ -5667,7 +5667,7 @@
         <v>0</v>
       </c>
       <c r="U42" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V42" t="n">
         <v>0</v>
@@ -5863,7 +5863,7 @@
         <v>0</v>
       </c>
       <c r="U43" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V43" t="n">
         <v>0</v>
@@ -6252,16 +6252,16 @@
         <v>10</v>
       </c>
       <c r="T45" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U45" t="n">
         <v>0</v>
       </c>
       <c r="V45" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="W45" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X45" t="n">
         <v>5</v>
@@ -6784,16 +6784,16 @@
         <v>120</v>
       </c>
       <c r="T48" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U48" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="V48" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="W48" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="X48" t="n">
         <v>36</v>

--- a/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_398_EL.xlsx
+++ b/informes_data/Euroleague/2025-26/playoffs/raw/boxscore_full_analysis_398_EL.xlsx
@@ -674,10 +674,10 @@
         <v>5</v>
       </c>
       <c r="N2" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="O2" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="P2" t="n">
         <v>3</v>
@@ -695,17 +695,17 @@
         <v>2</v>
       </c>
       <c r="U2" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="V2" t="n">
         <v>6</v>
       </c>
       <c r="W2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>72.73</t>
+          <t>61.29</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
@@ -720,17 +720,17 @@
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>50.00</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>35.29</t>
+          <t>37.50</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
@@ -833,10 +833,10 @@
         <v>16</v>
       </c>
       <c r="N3" t="n">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="O3" t="n">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="P3" t="n">
         <v>4</v>
@@ -854,17 +854,17 @@
         <v>2</v>
       </c>
       <c r="U3" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="V3" t="n">
         <v>5</v>
       </c>
       <c r="W3" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>83.72</t>
+          <t>75.86</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
@@ -879,17 +879,17 @@
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>100.00</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>27.78</t>
+          <t>29.41</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>1.67</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
@@ -1543,14 +1543,14 @@
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y18" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA18" t="n">
@@ -1739,14 +1739,14 @@
         <v>2</v>
       </c>
       <c r="X19" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Y19" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>71.4%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AA19" t="n">
@@ -2915,14 +2915,14 @@
         <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="Y25" t="n">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA25" t="n">
@@ -3147,7 +3147,7 @@
         <v>0</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI26" t="inlineStr">
         <is>
@@ -3158,7 +3158,7 @@
         <v>0</v>
       </c>
       <c r="AK26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AL26" t="inlineStr">
         <is>
@@ -3307,14 +3307,14 @@
         <v>3</v>
       </c>
       <c r="X27" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Y27" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>81.2%</t>
+          <t>80.0%</t>
         </is>
       </c>
       <c r="AA27" t="n">
@@ -3839,14 +3839,14 @@
         <v>6</v>
       </c>
       <c r="X30" t="n">
-        <v>32</v>
+        <v>19</v>
       </c>
       <c r="Y30" t="n">
-        <v>44</v>
+        <v>31</v>
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>72.7%</t>
+          <t>61.3%</t>
         </is>
       </c>
       <c r="AA30" t="n">
@@ -3875,22 +3875,22 @@
         <v>2</v>
       </c>
       <c r="AH30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AJ30" t="n">
         <v>6</v>
       </c>
       <c r="AK30" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL30" t="inlineStr">
         <is>
-          <t>35.3%</t>
+          <t>37.5%</t>
         </is>
       </c>
       <c r="AM30" t="inlineStr">
@@ -4536,7 +4536,7 @@
         <v>0</v>
       </c>
       <c r="AH36" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI36" t="inlineStr">
         <is>
@@ -4547,7 +4547,7 @@
         <v>0</v>
       </c>
       <c r="AK36" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AL36" t="inlineStr">
         <is>
@@ -4696,14 +4696,14 @@
         <v>1</v>
       </c>
       <c r="X37" t="n">
+        <v>2</v>
+      </c>
+      <c r="Y37" t="n">
         <v>3</v>
       </c>
-      <c r="Y37" t="n">
-        <v>4</v>
-      </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA37" t="n">
@@ -4892,14 +4892,14 @@
         <v>0</v>
       </c>
       <c r="X38" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Y38" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>50.0%</t>
         </is>
       </c>
       <c r="AA38" t="n">
@@ -5284,14 +5284,14 @@
         <v>1</v>
       </c>
       <c r="X40" t="n">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="Y40" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>87.5%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA40" t="n">
@@ -5480,14 +5480,14 @@
         <v>3</v>
       </c>
       <c r="X41" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="Y41" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>83.3%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AA41" t="n">
@@ -6264,10 +6264,10 @@
         <v>2</v>
       </c>
       <c r="X45" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Y45" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Z45" t="inlineStr">
         <is>
@@ -6460,14 +6460,14 @@
         <v>0</v>
       </c>
       <c r="X46" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y46" t="n">
         <v>3</v>
       </c>
-      <c r="Y46" t="n">
-        <v>5</v>
-      </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>60.0%</t>
+          <t>33.3%</t>
         </is>
       </c>
       <c r="AA46" t="n">
@@ -6796,14 +6796,14 @@
         <v>8</v>
       </c>
       <c r="X48" t="n">
-        <v>36</v>
+        <v>22</v>
       </c>
       <c r="Y48" t="n">
-        <v>43</v>
+        <v>29</v>
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>83.7%</t>
+          <t>75.9%</t>
         </is>
       </c>
       <c r="AA48" t="n">
@@ -6832,22 +6832,22 @@
         <v>2</v>
       </c>
       <c r="AH48" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AI48" t="inlineStr">
         <is>
-          <t>100.0%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="AJ48" t="n">
         <v>5</v>
       </c>
       <c r="AK48" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AL48" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="AM48" t="inlineStr">
